--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29AE965-A655-4E0E-9392-FB4A6EF1A151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F93F5CD-D0A6-4EF3-8FAC-4844979833F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F93F5CD-D0A6-4EF3-8FAC-4844979833F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B98817-A907-47B1-B8FA-D2851379A61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="exiobase" sheetId="1" r:id="rId1"/>
+    <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
     <sheet name="map" sheetId="4" r:id="rId2"/>
-    <sheet name="german" sheetId="2" r:id="rId3"/>
-    <sheet name="english" sheetId="3" r:id="rId4"/>
+    <sheet name="Deutsch" sheetId="2" r:id="rId3"/>
+    <sheet name="Englisch" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B98817-A907-47B1-B8FA-D2851379A61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7FEF61-765E-4B4D-B246-E3448DB1027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="298">
   <si>
     <t>region</t>
   </si>
@@ -914,6 +914,9 @@
   </si>
   <si>
     <t>eSwatini</t>
+  </si>
+  <si>
+    <t>continent</t>
   </si>
 </sst>
 </file>
@@ -3428,10 +3431,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7FEF61-765E-4B4D-B246-E3448DB1027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4325E11-82FB-4E5E-AD07-8CDE4FACBE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
-    <sheet name="map" sheetId="4" r:id="rId2"/>
-    <sheet name="Deutsch" sheetId="2" r:id="rId3"/>
-    <sheet name="Englisch" sheetId="3" r:id="rId4"/>
+    <sheet name="Deutsch" sheetId="2" r:id="rId2"/>
+    <sheet name="English" sheetId="3" r:id="rId3"/>
+    <sheet name="Français" sheetId="6" r:id="rId4"/>
+    <sheet name="Español" sheetId="7" r:id="rId5"/>
+    <sheet name="map" sheetId="4" r:id="rId6"/>
+    <sheet name="population" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="397">
   <si>
     <t>region</t>
   </si>
@@ -917,6 +920,303 @@
   </si>
   <si>
     <t>continent</t>
+  </si>
+  <si>
+    <t>population</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> continent</t>
+  </si>
+  <si>
+    <t>région</t>
+  </si>
+  <si>
+    <t>Autriche</t>
+  </si>
+  <si>
+    <t>Belgique</t>
+  </si>
+  <si>
+    <t>Bulgarie</t>
+  </si>
+  <si>
+    <t>Chypre</t>
+  </si>
+  <si>
+    <t>Tchéquie</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>Danemark</t>
+  </si>
+  <si>
+    <t>Estonie</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>Finlande</t>
+  </si>
+  <si>
+    <t>Grèce</t>
+  </si>
+  <si>
+    <t>Croatie</t>
+  </si>
+  <si>
+    <t>Hongrie</t>
+  </si>
+  <si>
+    <t>Irlande</t>
+  </si>
+  <si>
+    <t>Italie</t>
+  </si>
+  <si>
+    <t>Lituanie</t>
+  </si>
+  <si>
+    <t>Lettonie</t>
+  </si>
+  <si>
+    <t>Malte</t>
+  </si>
+  <si>
+    <t>Pays-Bas</t>
+  </si>
+  <si>
+    <t>Pologne</t>
+  </si>
+  <si>
+    <t>Roumanie</t>
+  </si>
+  <si>
+    <t>Suède</t>
+  </si>
+  <si>
+    <t>Slovénie</t>
+  </si>
+  <si>
+    <t>Slovaquie</t>
+  </si>
+  <si>
+    <t>Royaume-Uni</t>
+  </si>
+  <si>
+    <t>États-Unis</t>
+  </si>
+  <si>
+    <t>Amérique du Nord</t>
+  </si>
+  <si>
+    <t>Japon</t>
+  </si>
+  <si>
+    <t>Asie</t>
+  </si>
+  <si>
+    <t>Chine</t>
+  </si>
+  <si>
+    <t>Corée du Sud</t>
+  </si>
+  <si>
+    <t>Brésil</t>
+  </si>
+  <si>
+    <t>Amérique du Sud</t>
+  </si>
+  <si>
+    <t>Inde</t>
+  </si>
+  <si>
+    <t>Mexique</t>
+  </si>
+  <si>
+    <t>Russie</t>
+  </si>
+  <si>
+    <t>Australie</t>
+  </si>
+  <si>
+    <t>Océanie</t>
+  </si>
+  <si>
+    <t>Suisse</t>
+  </si>
+  <si>
+    <t>Turquie</t>
+  </si>
+  <si>
+    <t>Taïwan</t>
+  </si>
+  <si>
+    <t>Norvège</t>
+  </si>
+  <si>
+    <t>Indonésie</t>
+  </si>
+  <si>
+    <t>Afrique du Sud</t>
+  </si>
+  <si>
+    <t>Afrique</t>
+  </si>
+  <si>
+    <t>Région du monde Asie</t>
+  </si>
+  <si>
+    <t>Région du monde Amérique latine</t>
+  </si>
+  <si>
+    <t>Région du monde Europe</t>
+  </si>
+  <si>
+    <t>Région du monde Afrique</t>
+  </si>
+  <si>
+    <t>región</t>
+  </si>
+  <si>
+    <t>continente</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Chipre</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Finlandia</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Grecia</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>Hungría</t>
+  </si>
+  <si>
+    <t>Irlanda</t>
+  </si>
+  <si>
+    <t>Italia</t>
+  </si>
+  <si>
+    <t>Lituania</t>
+  </si>
+  <si>
+    <t>Luxemburgo</t>
+  </si>
+  <si>
+    <t>Letonia</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>Polonia</t>
+  </si>
+  <si>
+    <t>Rumanía</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Eslovenia</t>
+  </si>
+  <si>
+    <t>Eslovaquia</t>
+  </si>
+  <si>
+    <t>Reino Unido</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>América del Norte</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>América del Sur</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Rusia</t>
+  </si>
+  <si>
+    <t>Oceanía</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>Taiwán</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>África</t>
+  </si>
+  <si>
+    <t>Región del mundo Asia</t>
+  </si>
+  <si>
+    <t>Región del mundo América Latina</t>
+  </si>
+  <si>
+    <t>Región del mundo Europa</t>
+  </si>
+  <si>
+    <t>Región del mundo África</t>
+  </si>
+  <si>
+    <t>Región del mundo Oriente Medio</t>
+  </si>
+  <si>
+    <t>Région du monde Moyen-Orient</t>
   </si>
 </sst>
 </file>
@@ -1561,6 +1861,1662 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89530307-67FA-48C2-ADA7-7C18C4451765}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B404786-AE17-4BD1-A975-DCF0ECE3DB3C}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B179"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3006,827 +4962,409 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54130B71-89B3-47B7-9AD0-D3A95FB56FB2}">
   <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>297</v>
+      <c r="B1" s="1" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>9120000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>108</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11820000</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>108</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>6450000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1360000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>10740000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>84550000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5980000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1370000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>47890000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>5620000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>66550000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>9940000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3860000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>9590000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>108</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5310000</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>58760000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>108</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2850000</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>108</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>681000</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>108</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1870000</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>108</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>545000</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>108</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>18230000</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>108</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>37560000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>108</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>10430000</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>19020000</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>108</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>10610000</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>108</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2120000</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>108</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5420000</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>108</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>69550000</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>134</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>345427000</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>123104000</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>135</v>
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1408281000</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>134</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>40127000</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>135</v>
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>51718000</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>139</v>
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>211999000</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>135</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1463866000</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>134</v>
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>131947000</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>135</v>
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>143997000</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>144</v>
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>26974000</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>8922000</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>135</v>
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>87686000</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>135</v>
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>23420000</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>108</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5576000</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>135</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>281190000</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>150</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>63212000</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>135</v>
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>876300000</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>139</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>449800000</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>92900000</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>150</v>
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>1444900000</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>293874618</v>
       </c>
     </row>
   </sheetData>

--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7FEF61-765E-4B4D-B246-E3448DB1027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1853F7-5E5A-45EA-A658-3E9800646ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
     <sheet name="map" sheetId="4" r:id="rId2"/>
     <sheet name="Deutsch" sheetId="2" r:id="rId3"/>
     <sheet name="Englisch" sheetId="3" r:id="rId4"/>
+    <sheet name="population" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="299">
   <si>
     <t>region</t>
   </si>
@@ -917,6 +918,9 @@
   </si>
   <si>
     <t>continent</t>
+  </si>
+  <si>
+    <t>population</t>
   </si>
 </sst>
 </file>
@@ -3832,4 +3836,267 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54130B71-89B3-47B7-9AD0-D3A95FB56FB2}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1853F7-5E5A-45EA-A658-3E9800646ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8669A5A5-06D0-44C9-BBE9-D1E89C9DD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3855,245 +3855,392 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="2">
+        <v>9120000</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="2">
+        <v>11820000</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="2">
+        <v>6450000</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B5" s="2">
+        <v>1360000</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B6" s="2">
+        <v>10740000</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B7" s="2">
+        <v>84550000</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="B8" s="2">
+        <v>5980000</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="B9" s="2">
+        <v>1370000</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="2">
+        <v>47890000</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B11" s="2">
+        <v>5620000</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B12" s="2">
+        <v>66550000</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="B13" s="2">
+        <v>9940000</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="B14" s="2">
+        <v>3860000</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="B15" s="2">
+        <v>9590000</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2">
+        <v>5310000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2">
+        <v>58760000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2">
+        <v>681000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>1870000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>545000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>18230000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>37560000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>10430000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" s="2">
+        <v>19020000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>10610000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
+        <v>2120000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>5420000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2">
+        <v>69550000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>345427000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2">
+        <v>123104000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>1408281000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2">
+        <v>40127000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>51718000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
+        <v>211999000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>1463866000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37" s="2">
+        <v>131947000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
+        <v>143997000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2">
+        <v>26974000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40" s="2">
+        <v>8922000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41" s="2">
+        <v>87686000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42" s="2">
+        <v>23420000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43" s="2">
+        <v>5576000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>281190000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45" s="2">
+        <v>63212000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>876300000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47" s="2">
+        <v>449800000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>92900000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" s="2">
+        <v>1444900000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>293874618</v>
       </c>
     </row>
   </sheetData>

--- a/config/regions.xlsx
+++ b/config/regions.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8669A5A5-06D0-44C9-BBE9-D1E89C9DD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4325E11-82FB-4E5E-AD07-8CDE4FACBE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
-    <sheet name="map" sheetId="4" r:id="rId2"/>
-    <sheet name="Deutsch" sheetId="2" r:id="rId3"/>
-    <sheet name="Englisch" sheetId="3" r:id="rId4"/>
-    <sheet name="population" sheetId="5" r:id="rId5"/>
+    <sheet name="Deutsch" sheetId="2" r:id="rId2"/>
+    <sheet name="English" sheetId="3" r:id="rId3"/>
+    <sheet name="Français" sheetId="6" r:id="rId4"/>
+    <sheet name="Español" sheetId="7" r:id="rId5"/>
+    <sheet name="map" sheetId="4" r:id="rId6"/>
+    <sheet name="population" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="397">
   <si>
     <t>region</t>
   </si>
@@ -921,6 +923,300 @@
   </si>
   <si>
     <t>population</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> continent</t>
+  </si>
+  <si>
+    <t>région</t>
+  </si>
+  <si>
+    <t>Autriche</t>
+  </si>
+  <si>
+    <t>Belgique</t>
+  </si>
+  <si>
+    <t>Bulgarie</t>
+  </si>
+  <si>
+    <t>Chypre</t>
+  </si>
+  <si>
+    <t>Tchéquie</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>Danemark</t>
+  </si>
+  <si>
+    <t>Estonie</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>Finlande</t>
+  </si>
+  <si>
+    <t>Grèce</t>
+  </si>
+  <si>
+    <t>Croatie</t>
+  </si>
+  <si>
+    <t>Hongrie</t>
+  </si>
+  <si>
+    <t>Irlande</t>
+  </si>
+  <si>
+    <t>Italie</t>
+  </si>
+  <si>
+    <t>Lituanie</t>
+  </si>
+  <si>
+    <t>Lettonie</t>
+  </si>
+  <si>
+    <t>Malte</t>
+  </si>
+  <si>
+    <t>Pays-Bas</t>
+  </si>
+  <si>
+    <t>Pologne</t>
+  </si>
+  <si>
+    <t>Roumanie</t>
+  </si>
+  <si>
+    <t>Suède</t>
+  </si>
+  <si>
+    <t>Slovénie</t>
+  </si>
+  <si>
+    <t>Slovaquie</t>
+  </si>
+  <si>
+    <t>Royaume-Uni</t>
+  </si>
+  <si>
+    <t>États-Unis</t>
+  </si>
+  <si>
+    <t>Amérique du Nord</t>
+  </si>
+  <si>
+    <t>Japon</t>
+  </si>
+  <si>
+    <t>Asie</t>
+  </si>
+  <si>
+    <t>Chine</t>
+  </si>
+  <si>
+    <t>Corée du Sud</t>
+  </si>
+  <si>
+    <t>Brésil</t>
+  </si>
+  <si>
+    <t>Amérique du Sud</t>
+  </si>
+  <si>
+    <t>Inde</t>
+  </si>
+  <si>
+    <t>Mexique</t>
+  </si>
+  <si>
+    <t>Russie</t>
+  </si>
+  <si>
+    <t>Australie</t>
+  </si>
+  <si>
+    <t>Océanie</t>
+  </si>
+  <si>
+    <t>Suisse</t>
+  </si>
+  <si>
+    <t>Turquie</t>
+  </si>
+  <si>
+    <t>Taïwan</t>
+  </si>
+  <si>
+    <t>Norvège</t>
+  </si>
+  <si>
+    <t>Indonésie</t>
+  </si>
+  <si>
+    <t>Afrique du Sud</t>
+  </si>
+  <si>
+    <t>Afrique</t>
+  </si>
+  <si>
+    <t>Région du monde Asie</t>
+  </si>
+  <si>
+    <t>Région du monde Amérique latine</t>
+  </si>
+  <si>
+    <t>Région du monde Europe</t>
+  </si>
+  <si>
+    <t>Région du monde Afrique</t>
+  </si>
+  <si>
+    <t>región</t>
+  </si>
+  <si>
+    <t>continente</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Chipre</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Finlandia</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Grecia</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>Hungría</t>
+  </si>
+  <si>
+    <t>Irlanda</t>
+  </si>
+  <si>
+    <t>Italia</t>
+  </si>
+  <si>
+    <t>Lituania</t>
+  </si>
+  <si>
+    <t>Luxemburgo</t>
+  </si>
+  <si>
+    <t>Letonia</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>Polonia</t>
+  </si>
+  <si>
+    <t>Rumanía</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Eslovenia</t>
+  </si>
+  <si>
+    <t>Eslovaquia</t>
+  </si>
+  <si>
+    <t>Reino Unido</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>América del Norte</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>América del Sur</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Rusia</t>
+  </si>
+  <si>
+    <t>Oceanía</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>Taiwán</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>África</t>
+  </si>
+  <si>
+    <t>Región del mundo Asia</t>
+  </si>
+  <si>
+    <t>Región del mundo América Latina</t>
+  </si>
+  <si>
+    <t>Región del mundo Europa</t>
+  </si>
+  <si>
+    <t>Región del mundo África</t>
+  </si>
+  <si>
+    <t>Región del mundo Oriente Medio</t>
+  </si>
+  <si>
+    <t>Région du monde Moyen-Orient</t>
   </si>
 </sst>
 </file>
@@ -1565,6 +1861,1662 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89530307-67FA-48C2-ADA7-7C18C4451765}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B404786-AE17-4BD1-A975-DCF0ECE3DB3C}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B179"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3010,835 +4962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54130B71-89B3-47B7-9AD0-D3A95FB56FB2}">
   <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
